--- a/Animals_Clearance_Turner_complete_list.xlsx
+++ b/Animals_Clearance_Turner_complete_list.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rja20/Documents/MATLAB/Bruker_radial_recon/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D561B20C-6067-F14B-AC78-C54A5F0E98C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F470FEC-3A97-AA48-ADCA-BC36265BD60F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4760" yWindow="2100" windowWidth="39980" windowHeight="26700" xr2:uid="{84E1B740-0BA9-6B4F-AA6B-2F5191EC9593}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$N$1:$N$58</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$L$1:$M$59</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">Sheet1!$A$1:$T$29</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">Sheet2!$A$1:$B$18</definedName>
   </definedNames>
@@ -3967,7 +3967,6 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="N1:N58" xr:uid="{FFA5DD44-FC73-C044-A196-AFED27C59F6D}"/>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="60" orientation="landscape" horizontalDpi="0" verticalDpi="0"/>

--- a/Animals_Clearance_Turner_complete_list.xlsx
+++ b/Animals_Clearance_Turner_complete_list.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rja20/Documents/MATLAB/Bruker_radial_recon/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F470FEC-3A97-AA48-ADCA-BC36265BD60F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B59DD78-984F-9447-AF42-9C0CAF82CF81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4760" yWindow="2100" windowWidth="39980" windowHeight="26700" xr2:uid="{84E1B740-0BA9-6B4F-AA6B-2F5191EC9593}"/>
   </bookViews>

--- a/Animals_Clearance_Turner_complete_list.xlsx
+++ b/Animals_Clearance_Turner_complete_list.xlsx
@@ -1,28 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10102"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10510"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rja20/Documents/MATLAB/Bruker_radial_recon/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bass/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B59DD78-984F-9447-AF42-9C0CAF82CF81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9D82124-6922-B644-9F6B-F804567EAF3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4760" yWindow="2100" windowWidth="39980" windowHeight="26700" xr2:uid="{84E1B740-0BA9-6B4F-AA6B-2F5191EC9593}"/>
+    <workbookView xWindow="4760" yWindow="560" windowWidth="39980" windowHeight="26700" xr2:uid="{84E1B740-0BA9-6B4F-AA6B-2F5191EC9593}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$L$1:$M$59</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$L$1:$M$73</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">Sheet1!$A$1:$T$29</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">Sheet2!$A$1:$B$18</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -43,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="482" uniqueCount="203">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="631" uniqueCount="254">
   <si>
     <t>Cohort_ID</t>
   </si>
@@ -671,12 +670,165 @@
   <si>
     <t>Needs coregistration, esp Block 2</t>
   </si>
+  <si>
+    <t>B26040803</t>
+  </si>
+  <si>
+    <t>B26040804</t>
+  </si>
+  <si>
+    <t>B26040801</t>
+  </si>
+  <si>
+    <t>B26041401</t>
+  </si>
+  <si>
+    <t>B26041601</t>
+  </si>
+  <si>
+    <t>B26041602</t>
+  </si>
+  <si>
+    <t>B26042200</t>
+  </si>
+  <si>
+    <t>B26042201</t>
+  </si>
+  <si>
+    <t>B25042300</t>
+  </si>
+  <si>
+    <t>B25042301</t>
+  </si>
+  <si>
+    <t>B26042900</t>
+  </si>
+  <si>
+    <t>B26042901</t>
+  </si>
+  <si>
+    <t>B26043000</t>
+  </si>
+  <si>
+    <t>B26043001</t>
+  </si>
+  <si>
+    <t>2.2G total</t>
+  </si>
+  <si>
+    <t>4.7G total</t>
+  </si>
+  <si>
+    <t>4.5G total</t>
+  </si>
+  <si>
+    <t>1.3G total</t>
+  </si>
+  <si>
+    <t>3.2G total</t>
+  </si>
+  <si>
+    <t>260408_2</t>
+  </si>
+  <si>
+    <t>260408_4</t>
+  </si>
+  <si>
+    <t>A26040804</t>
+  </si>
+  <si>
+    <t>P26040804</t>
+  </si>
+  <si>
+    <t>260408_3</t>
+  </si>
+  <si>
+    <t>Died 30 minutes before end of study</t>
+  </si>
+  <si>
+    <t>Two RARE images, with 44 being 1/2 the size of 34</t>
+  </si>
+  <si>
+    <t>260408_1</t>
+  </si>
+  <si>
+    <t>A26040802</t>
+  </si>
+  <si>
+    <t>A26040803</t>
+  </si>
+  <si>
+    <t>A26040801</t>
+  </si>
+  <si>
+    <t>Blocks 1 and 2 appear to be incomplete or missing</t>
+  </si>
+  <si>
+    <t>260414_1</t>
+  </si>
+  <si>
+    <t>A26041401</t>
+  </si>
+  <si>
+    <t>A26041601</t>
+  </si>
+  <si>
+    <t>260416_1</t>
+  </si>
+  <si>
+    <t>260416_2</t>
+  </si>
+  <si>
+    <t>A26041602</t>
+  </si>
+  <si>
+    <t>Block 2 missing?</t>
+  </si>
+  <si>
+    <t>260422_1</t>
+  </si>
+  <si>
+    <t>C26042201</t>
+  </si>
+  <si>
+    <t>260422_2</t>
+  </si>
+  <si>
+    <t>C26042202</t>
+  </si>
+  <si>
+    <t>V26042201</t>
+  </si>
+  <si>
+    <t>Died during Block 2</t>
+  </si>
+  <si>
+    <t>V26042202</t>
+  </si>
+  <si>
+    <t>260423_1</t>
+  </si>
+  <si>
+    <t>C26042301</t>
+  </si>
+  <si>
+    <t>V26042301</t>
+  </si>
+  <si>
+    <t>260423_2</t>
+  </si>
+  <si>
+    <t>C26042302</t>
+  </si>
+  <si>
+    <t>V26042302</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -707,6 +859,12 @@
       <sz val="8"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -757,7 +915,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -794,6 +952,7 @@
     <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="14" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="2" fontId="2" fillId="2" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1131,7 +1290,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AW59"/>
+  <dimension ref="A1:AW73"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="19" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.6640625" style="13" customWidth="1"/>
@@ -3601,368 +3760,1178 @@
       </c>
       <c r="AB39" s="16"/>
     </row>
-    <row r="45" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A45" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B45" s="2"/>
-      <c r="C45" s="2"/>
-      <c r="D45" s="2" t="s">
-        <v>41</v>
-      </c>
+    <row r="40" spans="1:28" s="28" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="K40" s="29"/>
+      <c r="O40" s="29"/>
+      <c r="Q40" s="29"/>
+      <c r="R40" s="16"/>
+      <c r="T40" s="16"/>
+      <c r="U40" s="20"/>
+      <c r="V40" s="20"/>
+      <c r="W40" s="20"/>
+      <c r="X40" s="20"/>
+      <c r="Y40" s="20"/>
+      <c r="Z40" s="16"/>
+      <c r="AA40" s="16"/>
+      <c r="AB40" s="16"/>
+    </row>
+    <row r="41" spans="1:28" s="28" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="K41" s="29"/>
+      <c r="O41" s="29"/>
+      <c r="Q41" s="29"/>
+      <c r="R41" s="16"/>
+      <c r="T41" s="16"/>
+      <c r="U41" s="20"/>
+      <c r="V41" s="20"/>
+      <c r="W41" s="20"/>
+      <c r="X41" s="20"/>
+      <c r="Y41" s="20"/>
+      <c r="Z41" s="16"/>
+      <c r="AA41" s="16"/>
+      <c r="AB41" s="16"/>
+    </row>
+    <row r="42" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="E42" s="13" t="s">
+        <v>222</v>
+      </c>
+      <c r="F42" s="13" t="s">
+        <v>222</v>
+      </c>
+      <c r="G42" s="13" t="s">
+        <v>222</v>
+      </c>
+      <c r="H42" s="13" t="s">
+        <v>230</v>
+      </c>
+      <c r="I42" s="13" t="s">
+        <v>217</v>
+      </c>
+      <c r="J42" s="13" t="s">
+        <v>222</v>
+      </c>
+      <c r="K42" s="33">
+        <v>46120</v>
+      </c>
+      <c r="L42" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="M42" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="N42" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="O42" s="33">
+        <v>45719</v>
+      </c>
+      <c r="P42" s="13">
+        <v>26</v>
+      </c>
+      <c r="U42" s="13">
+        <v>45</v>
+      </c>
+      <c r="V42" s="13">
+        <v>46</v>
+      </c>
+      <c r="X42" s="13">
+        <v>44</v>
+      </c>
+      <c r="AA42" s="13" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="43" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="E43" s="13" t="s">
+        <v>226</v>
+      </c>
+      <c r="F43" s="13" t="s">
+        <v>226</v>
+      </c>
+      <c r="G43" s="13" t="s">
+        <v>203</v>
+      </c>
+      <c r="H43" s="13" t="s">
+        <v>231</v>
+      </c>
+      <c r="I43" s="13" t="s">
+        <v>218</v>
+      </c>
+      <c r="J43" s="13" t="s">
+        <v>226</v>
+      </c>
+      <c r="K43" s="33">
+        <v>46120</v>
+      </c>
+      <c r="L43" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="M43" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="N43" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="O43" s="33">
+        <v>45719</v>
+      </c>
+      <c r="P43" s="13">
+        <v>26</v>
+      </c>
+      <c r="U43" s="13">
+        <v>8</v>
+      </c>
+      <c r="V43" s="13">
+        <v>9</v>
+      </c>
+      <c r="W43" s="13">
+        <v>10</v>
+      </c>
+      <c r="X43" s="13">
+        <v>7</v>
+      </c>
+      <c r="AA43" s="13" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="44" spans="1:28" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E44" s="13" t="s">
+        <v>223</v>
+      </c>
+      <c r="F44" s="13" t="s">
+        <v>223</v>
+      </c>
+      <c r="G44" s="13" t="s">
+        <v>204</v>
+      </c>
+      <c r="H44" s="13" t="s">
+        <v>224</v>
+      </c>
+      <c r="I44" s="13" t="s">
+        <v>219</v>
+      </c>
+      <c r="J44" s="13" t="s">
+        <v>223</v>
+      </c>
+      <c r="K44" s="33">
+        <v>46121</v>
+      </c>
+      <c r="L44" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="M44" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="N44" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="O44" s="33">
+        <v>45805</v>
+      </c>
+      <c r="P44" s="13">
+        <v>29</v>
+      </c>
+      <c r="Q44" s="33">
+        <v>46121</v>
+      </c>
+      <c r="U44" s="13">
+        <v>30</v>
+      </c>
+      <c r="V44" s="13">
+        <v>29</v>
+      </c>
+      <c r="W44" s="13">
+        <v>28</v>
+      </c>
+      <c r="X44" s="13">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="45" spans="1:28" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E45" s="13" t="s">
-        <v>137</v>
+        <v>229</v>
       </c>
       <c r="F45" s="13" t="s">
-        <v>137</v>
+        <v>229</v>
       </c>
       <c r="G45" s="13" t="s">
-        <v>135</v>
+        <v>205</v>
+      </c>
+      <c r="H45" s="13" t="s">
+        <v>232</v>
+      </c>
+      <c r="I45" s="13" t="s">
+        <v>220</v>
       </c>
       <c r="J45" s="13" t="s">
-        <v>143</v>
+        <v>229</v>
       </c>
       <c r="K45" s="33">
-        <v>45939</v>
+        <v>46121</v>
       </c>
       <c r="L45" s="13" t="s">
-        <v>136</v>
+        <v>67</v>
+      </c>
+      <c r="M45" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="N45" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="O45" s="33">
+        <v>45748</v>
+      </c>
+      <c r="P45" s="13">
+        <v>29</v>
+      </c>
+      <c r="U45" s="13">
+        <v>10</v>
+      </c>
+      <c r="V45" s="13">
+        <v>11</v>
+      </c>
+      <c r="W45" s="13">
+        <v>12</v>
+      </c>
+      <c r="X45" s="13">
+        <v>5</v>
       </c>
       <c r="AA45" s="13" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="46" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A46" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B46" s="2"/>
-      <c r="C46" s="2"/>
-      <c r="D46" s="2" t="s">
-        <v>41</v>
-      </c>
+        <v>233</v>
+      </c>
+    </row>
+    <row r="46" spans="1:28" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E46" s="13" t="s">
-        <v>141</v>
+        <v>223</v>
       </c>
       <c r="F46" s="13" t="s">
-        <v>141</v>
+        <v>223</v>
       </c>
       <c r="G46" s="13" t="s">
-        <v>140</v>
+        <v>204</v>
+      </c>
+      <c r="H46" s="13" t="s">
+        <v>225</v>
+      </c>
+      <c r="I46" s="13" t="s">
+        <v>219</v>
       </c>
       <c r="J46" s="13" t="s">
-        <v>141</v>
+        <v>223</v>
       </c>
       <c r="K46" s="33">
-        <v>45946</v>
+        <v>46126</v>
       </c>
       <c r="L46" s="13" t="s">
-        <v>136</v>
-      </c>
-      <c r="AA46" s="13" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="47" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A47" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B47" s="2"/>
-      <c r="C47" s="2"/>
-      <c r="D47" s="2" t="s">
-        <v>41</v>
-      </c>
+        <v>68</v>
+      </c>
+      <c r="M46" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="N46" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="O46" s="33">
+        <v>45805</v>
+      </c>
+      <c r="P46" s="13">
+        <v>29</v>
+      </c>
+      <c r="U46" s="13">
+        <v>10</v>
+      </c>
+      <c r="V46" s="13">
+        <v>11</v>
+      </c>
+      <c r="W46" s="13">
+        <v>12</v>
+      </c>
+      <c r="X46" s="13">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="47" spans="1:28" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E47" s="13" t="s">
-        <v>145</v>
+        <v>234</v>
       </c>
       <c r="F47" s="13" t="s">
-        <v>145</v>
+        <v>234</v>
       </c>
       <c r="G47" s="13" t="s">
-        <v>144</v>
+        <v>206</v>
+      </c>
+      <c r="H47" s="13" t="s">
+        <v>235</v>
+      </c>
+      <c r="I47" s="13" t="s">
+        <v>219</v>
       </c>
       <c r="J47" s="13" t="s">
-        <v>145</v>
+        <v>234</v>
       </c>
       <c r="K47" s="33">
-        <v>45960</v>
+        <v>46126</v>
       </c>
       <c r="L47" s="13" t="s">
-        <v>136</v>
-      </c>
-      <c r="AA47" s="13" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="48" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A48" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B48" s="2"/>
-      <c r="C48" s="2"/>
-      <c r="D48" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="E48" s="13" t="s">
-        <v>146</v>
-      </c>
-      <c r="F48" s="13" t="s">
-        <v>146</v>
+        <v>67</v>
+      </c>
+      <c r="M47" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="N47" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="O47" s="33">
+        <v>45835</v>
+      </c>
+      <c r="P47" s="13">
+        <v>28</v>
+      </c>
+      <c r="U47" s="13">
+        <v>10</v>
+      </c>
+      <c r="V47" s="13">
+        <v>18</v>
+      </c>
+      <c r="W47" s="13">
+        <v>12</v>
+      </c>
+      <c r="X47" s="13">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="48" spans="1:28" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E48" s="36" t="s">
+        <v>237</v>
+      </c>
+      <c r="F48" s="36" t="s">
+        <v>237</v>
       </c>
       <c r="G48" s="13" t="s">
-        <v>147</v>
-      </c>
-      <c r="J48" s="13" t="s">
-        <v>146</v>
+        <v>207</v>
+      </c>
+      <c r="H48" s="13" t="s">
+        <v>236</v>
+      </c>
+      <c r="I48" s="13" t="s">
+        <v>219</v>
+      </c>
+      <c r="J48" s="36" t="s">
+        <v>237</v>
       </c>
       <c r="K48" s="33">
-        <v>46002</v>
+        <v>46128</v>
       </c>
       <c r="L48" s="13" t="s">
-        <v>136</v>
+        <v>67</v>
       </c>
       <c r="M48" s="13" t="s">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="N48" s="13" t="s">
         <v>36</v>
       </c>
       <c r="O48" s="33">
+        <v>45719</v>
+      </c>
+      <c r="P48" s="13">
+        <v>31</v>
+      </c>
+      <c r="U48" s="13">
+        <v>10</v>
+      </c>
+      <c r="V48" s="13">
+        <v>11</v>
+      </c>
+      <c r="W48" s="13">
+        <v>12</v>
+      </c>
+      <c r="X48" s="13">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="49" spans="1:27" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E49" s="13" t="s">
+        <v>238</v>
+      </c>
+      <c r="F49" s="13" t="s">
+        <v>238</v>
+      </c>
+      <c r="G49" s="13" t="s">
+        <v>208</v>
+      </c>
+      <c r="H49" s="36" t="s">
+        <v>239</v>
+      </c>
+      <c r="I49" s="13" t="s">
+        <v>217</v>
+      </c>
+      <c r="J49" s="13" t="s">
+        <v>238</v>
+      </c>
+      <c r="K49" s="33">
+        <v>46128</v>
+      </c>
+      <c r="L49" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="M49" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="N49" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="U49" s="13">
+        <v>10</v>
+      </c>
+      <c r="V49" s="13">
+        <v>19</v>
+      </c>
+      <c r="X49" s="13">
+        <v>5</v>
+      </c>
+      <c r="AA49" s="13" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="50" spans="1:27" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E50" s="13" t="s">
+        <v>241</v>
+      </c>
+      <c r="F50" s="13" t="s">
+        <v>241</v>
+      </c>
+      <c r="G50" s="13" t="s">
+        <v>209</v>
+      </c>
+      <c r="H50" s="13" t="s">
+        <v>242</v>
+      </c>
+      <c r="I50" s="13" t="s">
+        <v>219</v>
+      </c>
+      <c r="J50" s="13" t="s">
+        <v>241</v>
+      </c>
+      <c r="K50" s="33">
+        <v>46134</v>
+      </c>
+      <c r="L50" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="M50" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="N50" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="P50" s="13">
+        <v>26</v>
+      </c>
+      <c r="U50" s="13">
+        <v>10</v>
+      </c>
+      <c r="V50" s="13">
+        <v>11</v>
+      </c>
+      <c r="W50" s="13">
+        <v>12</v>
+      </c>
+      <c r="X50" s="13">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="51" spans="1:27" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E51" s="13" t="s">
+        <v>243</v>
+      </c>
+      <c r="F51" s="13" t="s">
+        <v>243</v>
+      </c>
+      <c r="G51" s="13" t="s">
+        <v>210</v>
+      </c>
+      <c r="H51" s="13" t="s">
+        <v>244</v>
+      </c>
+      <c r="I51" s="13" t="s">
+        <v>219</v>
+      </c>
+      <c r="J51" s="13" t="s">
+        <v>243</v>
+      </c>
+      <c r="K51" s="33">
+        <v>46134</v>
+      </c>
+      <c r="L51" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="M51" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="N51" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="P51" s="13">
+        <v>20</v>
+      </c>
+      <c r="U51" s="13">
+        <v>10</v>
+      </c>
+      <c r="V51" s="13">
+        <v>19</v>
+      </c>
+      <c r="W51" s="13">
+        <v>12</v>
+      </c>
+      <c r="X51" s="13">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="52" spans="1:27" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E52" s="13" t="s">
+        <v>248</v>
+      </c>
+      <c r="F52" s="13" t="s">
+        <v>248</v>
+      </c>
+      <c r="G52" s="13" t="s">
+        <v>211</v>
+      </c>
+      <c r="H52" s="13" t="s">
+        <v>249</v>
+      </c>
+      <c r="I52" s="13" t="s">
+        <v>219</v>
+      </c>
+      <c r="J52" s="13" t="s">
+        <v>248</v>
+      </c>
+      <c r="K52" s="33">
+        <v>46135</v>
+      </c>
+      <c r="L52" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="M52" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="N52" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="P52" s="13">
+        <v>31</v>
+      </c>
+      <c r="U52" s="13">
+        <v>10</v>
+      </c>
+      <c r="V52" s="13">
+        <v>11</v>
+      </c>
+      <c r="W52" s="13">
+        <v>12</v>
+      </c>
+      <c r="X52" s="13">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="53" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="E53" s="13" t="s">
+        <v>251</v>
+      </c>
+      <c r="F53" s="13" t="s">
+        <v>251</v>
+      </c>
+      <c r="G53" s="13" t="s">
+        <v>212</v>
+      </c>
+      <c r="H53" s="13" t="s">
+        <v>252</v>
+      </c>
+      <c r="I53" s="13" t="s">
+        <v>219</v>
+      </c>
+      <c r="J53" s="13" t="s">
+        <v>251</v>
+      </c>
+      <c r="K53" s="33">
+        <v>46135</v>
+      </c>
+      <c r="L53" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="M53" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="N53" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="P53" s="13">
+        <v>34</v>
+      </c>
+      <c r="U53" s="13">
+        <v>10</v>
+      </c>
+      <c r="V53" s="13">
+        <v>11</v>
+      </c>
+      <c r="W53" s="13">
+        <v>12</v>
+      </c>
+      <c r="X53" s="13">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="54" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="E54" s="13" t="s">
+        <v>241</v>
+      </c>
+      <c r="F54" s="13" t="s">
+        <v>241</v>
+      </c>
+      <c r="G54" s="13" t="s">
+        <v>213</v>
+      </c>
+      <c r="H54" s="13" t="s">
+        <v>245</v>
+      </c>
+      <c r="I54" s="13" t="s">
+        <v>221</v>
+      </c>
+      <c r="J54" s="13" t="s">
+        <v>241</v>
+      </c>
+      <c r="K54" s="33">
+        <v>46141</v>
+      </c>
+      <c r="L54" s="13" t="s">
+        <v>68</v>
+      </c>
+      <c r="M54" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="N54" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="P54" s="13">
+        <v>26</v>
+      </c>
+      <c r="U54" s="13">
+        <v>10</v>
+      </c>
+      <c r="V54" s="13">
+        <v>11</v>
+      </c>
+      <c r="X54" s="13">
+        <v>5</v>
+      </c>
+      <c r="AA54" s="13" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="55" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="E55" s="13" t="s">
+        <v>243</v>
+      </c>
+      <c r="F55" s="13" t="s">
+        <v>243</v>
+      </c>
+      <c r="G55" s="13" t="s">
+        <v>214</v>
+      </c>
+      <c r="H55" s="13" t="s">
+        <v>247</v>
+      </c>
+      <c r="I55" s="13" t="s">
+        <v>219</v>
+      </c>
+      <c r="J55" s="13" t="s">
+        <v>243</v>
+      </c>
+      <c r="K55" s="33">
+        <v>46141</v>
+      </c>
+      <c r="L55" s="13" t="s">
+        <v>68</v>
+      </c>
+      <c r="M55" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="N55" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="P55" s="13">
+        <v>20</v>
+      </c>
+      <c r="U55" s="13">
+        <v>10</v>
+      </c>
+      <c r="V55" s="13">
+        <v>11</v>
+      </c>
+      <c r="W55" s="13">
+        <v>12</v>
+      </c>
+      <c r="X55" s="13">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="56" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="E56" s="13" t="s">
+        <v>248</v>
+      </c>
+      <c r="F56" s="13" t="s">
+        <v>248</v>
+      </c>
+      <c r="G56" s="13" t="s">
+        <v>215</v>
+      </c>
+      <c r="H56" s="13" t="s">
+        <v>250</v>
+      </c>
+      <c r="I56" s="13" t="s">
+        <v>219</v>
+      </c>
+      <c r="J56" s="13" t="s">
+        <v>248</v>
+      </c>
+      <c r="K56" s="33">
+        <v>46142</v>
+      </c>
+      <c r="L56" s="13" t="s">
+        <v>68</v>
+      </c>
+      <c r="M56" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="N56" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="P56" s="13">
+        <v>31</v>
+      </c>
+      <c r="U56" s="13">
+        <v>10</v>
+      </c>
+      <c r="V56" s="13">
+        <v>11</v>
+      </c>
+      <c r="W56" s="13">
+        <v>12</v>
+      </c>
+      <c r="X56" s="13">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="57" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="E57" s="13" t="s">
+        <v>251</v>
+      </c>
+      <c r="F57" s="13" t="s">
+        <v>251</v>
+      </c>
+      <c r="G57" s="13" t="s">
+        <v>216</v>
+      </c>
+      <c r="H57" s="13" t="s">
+        <v>253</v>
+      </c>
+      <c r="I57" s="13" t="s">
+        <v>219</v>
+      </c>
+      <c r="J57" s="13" t="s">
+        <v>251</v>
+      </c>
+      <c r="K57" s="33">
+        <v>46142</v>
+      </c>
+      <c r="L57" s="13" t="s">
+        <v>68</v>
+      </c>
+      <c r="M57" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="N57" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="P57" s="13">
+        <v>34</v>
+      </c>
+      <c r="U57" s="13">
+        <v>10</v>
+      </c>
+      <c r="V57" s="13">
+        <v>11</v>
+      </c>
+      <c r="W57" s="13">
+        <v>12</v>
+      </c>
+      <c r="X57" s="13">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="59" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A59" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B59" s="2"/>
+      <c r="C59" s="2"/>
+      <c r="D59" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E59" s="13" t="s">
+        <v>137</v>
+      </c>
+      <c r="F59" s="13" t="s">
+        <v>137</v>
+      </c>
+      <c r="G59" s="13" t="s">
+        <v>135</v>
+      </c>
+      <c r="J59" s="13" t="s">
+        <v>143</v>
+      </c>
+      <c r="K59" s="33">
+        <v>45939</v>
+      </c>
+      <c r="L59" s="13" t="s">
+        <v>136</v>
+      </c>
+      <c r="AA59" s="13" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="60" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A60" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B60" s="2"/>
+      <c r="C60" s="2"/>
+      <c r="D60" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E60" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="F60" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="G60" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="J60" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="K60" s="33">
+        <v>45946</v>
+      </c>
+      <c r="L60" s="13" t="s">
+        <v>136</v>
+      </c>
+      <c r="AA60" s="13" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="61" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A61" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B61" s="2"/>
+      <c r="C61" s="2"/>
+      <c r="D61" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E61" s="13" t="s">
+        <v>145</v>
+      </c>
+      <c r="F61" s="13" t="s">
+        <v>145</v>
+      </c>
+      <c r="G61" s="13" t="s">
+        <v>144</v>
+      </c>
+      <c r="J61" s="13" t="s">
+        <v>145</v>
+      </c>
+      <c r="K61" s="33">
+        <v>45960</v>
+      </c>
+      <c r="L61" s="13" t="s">
+        <v>136</v>
+      </c>
+      <c r="AA61" s="13" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="62" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A62" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B62" s="2"/>
+      <c r="C62" s="2"/>
+      <c r="D62" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E62" s="13" t="s">
+        <v>146</v>
+      </c>
+      <c r="F62" s="13" t="s">
+        <v>146</v>
+      </c>
+      <c r="G62" s="13" t="s">
+        <v>147</v>
+      </c>
+      <c r="H62" s="31" t="s">
+        <v>154</v>
+      </c>
+      <c r="J62" s="13" t="s">
+        <v>146</v>
+      </c>
+      <c r="K62" s="33">
+        <v>46002</v>
+      </c>
+      <c r="L62" s="13" t="s">
+        <v>136</v>
+      </c>
+      <c r="M62" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="N62" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="O62" s="33">
         <v>45761</v>
       </c>
-      <c r="P48" s="13">
+      <c r="P62" s="13">
         <v>28</v>
       </c>
-      <c r="AA48" s="13" t="s">
+      <c r="AA62" s="13" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="49" spans="1:27" s="31" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="6" t="s">
+    <row r="63" spans="1:27" s="31" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A63" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="B49" s="6"/>
-      <c r="C49" s="6"/>
-      <c r="D49" s="6" t="s">
+      <c r="B63" s="6"/>
+      <c r="C63" s="6"/>
+      <c r="D63" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="E49" s="31" t="s">
+      <c r="E63" s="31" t="s">
         <v>148</v>
       </c>
-      <c r="F49" s="31" t="s">
+      <c r="F63" s="31" t="s">
         <v>148</v>
       </c>
-      <c r="G49" s="31" t="s">
+      <c r="G63" s="31" t="s">
         <v>149</v>
       </c>
-      <c r="H49" s="31" t="s">
-        <v>154</v>
-      </c>
-      <c r="J49" s="31" t="s">
+      <c r="H63" s="31" t="s">
+        <v>164</v>
+      </c>
+      <c r="J63" s="31" t="s">
         <v>148</v>
       </c>
-      <c r="K49" s="34">
+      <c r="K63" s="34">
         <v>46002</v>
       </c>
-      <c r="L49" s="31" t="s">
+      <c r="L63" s="31" t="s">
         <v>67</v>
       </c>
-      <c r="M49" s="31" t="s">
+      <c r="M63" s="31" t="s">
         <v>27</v>
       </c>
-      <c r="N49" s="31" t="s">
+      <c r="N63" s="31" t="s">
         <v>36</v>
       </c>
-      <c r="O49" s="34">
+      <c r="O63" s="34">
         <v>45761</v>
       </c>
-      <c r="P49" s="31">
+      <c r="P63" s="31">
         <v>25</v>
       </c>
-      <c r="U49" s="31" t="s">
+      <c r="U63" s="31" t="s">
         <v>176</v>
       </c>
-      <c r="V49" s="31">
+      <c r="V63" s="31">
         <v>8</v>
       </c>
-      <c r="W49" s="31">
+      <c r="W63" s="31">
         <v>9</v>
       </c>
-      <c r="X49" s="31">
+      <c r="X63" s="31">
         <v>2</v>
       </c>
-      <c r="Y49" s="18" t="s">
+      <c r="Y63" s="18" t="s">
         <v>178</v>
       </c>
-      <c r="AA49" s="31" t="s">
+      <c r="AA63" s="31" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="50" spans="1:27" s="31" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="6" t="s">
+    <row r="64" spans="1:27" s="31" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A64" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="B50" s="6"/>
-      <c r="C50" s="6"/>
-      <c r="D50" s="6" t="s">
+      <c r="B64" s="6"/>
+      <c r="C64" s="6"/>
+      <c r="D64" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="E50" s="31" t="s">
+      <c r="E64" s="31" t="s">
         <v>148</v>
       </c>
-      <c r="F50" s="31" t="s">
+      <c r="F64" s="31" t="s">
         <v>148</v>
       </c>
-      <c r="G50" s="31" t="s">
+      <c r="G64" s="31" t="s">
         <v>153</v>
       </c>
-      <c r="H50" s="31" t="s">
-        <v>164</v>
-      </c>
-      <c r="J50" s="31" t="s">
+      <c r="H64" s="13"/>
+      <c r="J64" s="31" t="s">
         <v>148</v>
       </c>
-      <c r="K50" s="34">
+      <c r="K64" s="34">
         <v>46009</v>
       </c>
-      <c r="L50" s="31" t="s">
+      <c r="L64" s="31" t="s">
         <v>68</v>
       </c>
-      <c r="M50" s="31" t="s">
+      <c r="M64" s="31" t="s">
         <v>27</v>
       </c>
-      <c r="N50" s="31" t="s">
+      <c r="N64" s="31" t="s">
         <v>36</v>
       </c>
-      <c r="P50" s="31">
+      <c r="P64" s="31">
         <v>27</v>
       </c>
-      <c r="U50" s="31">
+      <c r="U64" s="31">
         <v>13</v>
       </c>
-      <c r="V50" s="31">
+      <c r="V64" s="31">
         <v>22</v>
       </c>
-      <c r="W50" s="31">
+      <c r="W64" s="31">
         <v>9</v>
       </c>
-      <c r="X50" s="31">
+      <c r="X64" s="31">
         <v>2</v>
       </c>
-      <c r="Y50" s="18" t="s">
+      <c r="Y64" s="18" t="s">
         <v>178</v>
       </c>
-      <c r="AA50" s="31" t="s">
+      <c r="AA64" s="31" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="54" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="M54" s="13" t="s">
+    <row r="68" spans="13:25" x14ac:dyDescent="0.25">
+      <c r="M68" s="13" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="55" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="M55" s="13" t="s">
+    <row r="69" spans="13:25" x14ac:dyDescent="0.25">
+      <c r="M69" s="13" t="s">
         <v>133</v>
       </c>
-      <c r="R55" s="13" t="s">
+      <c r="R69" s="13" t="s">
         <v>130</v>
       </c>
-      <c r="Y55" s="13"/>
-    </row>
-    <row r="56" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="N56" s="13" t="s">
+      <c r="Y69" s="13"/>
+    </row>
+    <row r="70" spans="13:25" x14ac:dyDescent="0.25">
+      <c r="N70" s="13" t="s">
         <v>131</v>
       </c>
-      <c r="P56" s="13" t="s">
+      <c r="P70" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="S56" s="13" t="s">
+      <c r="S70" s="13" t="s">
         <v>131</v>
       </c>
-      <c r="Y56" s="13" t="s">
+      <c r="Y70" s="13" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="57" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="M57" s="13" t="s">
+    <row r="71" spans="13:25" x14ac:dyDescent="0.25">
+      <c r="M71" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="N57" s="13">
+      <c r="N71" s="13">
         <v>5</v>
       </c>
-      <c r="O57" s="13" t="s">
+      <c r="O71" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="P57" s="13">
+      <c r="P71" s="13">
         <v>3</v>
       </c>
-      <c r="R57" s="13" t="s">
+      <c r="R71" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="S57" s="13">
+      <c r="S71" s="13">
         <v>4</v>
       </c>
-      <c r="T57" s="13" t="s">
+      <c r="T71" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="Y57" s="13">
+      <c r="Y71" s="13">
         <v>3</v>
       </c>
     </row>
-    <row r="58" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="M58" s="13" t="s">
+    <row r="72" spans="13:25" x14ac:dyDescent="0.25">
+      <c r="M72" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="N58" s="13">
+      <c r="N72" s="13">
         <v>3</v>
       </c>
-      <c r="O58" s="13" t="s">
+      <c r="O72" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="P58" s="13">
+      <c r="P72" s="13">
         <v>4</v>
       </c>
-      <c r="R58" s="13" t="s">
+      <c r="R72" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="S58" s="13">
+      <c r="S72" s="13">
         <v>3</v>
       </c>
-      <c r="T58" s="13" t="s">
+      <c r="T72" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="Y58" s="13">
+      <c r="Y72" s="13">
         <v>5</v>
       </c>
     </row>
-    <row r="59" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="M59" s="13" t="s">
+    <row r="73" spans="13:25" x14ac:dyDescent="0.25">
+      <c r="M73" s="13" t="s">
         <v>132</v>
       </c>
-      <c r="N59" s="13">
-        <f>SUBTOTAL(9,N57:N58)</f>
+      <c r="N73" s="13">
+        <f>SUBTOTAL(9,N71:N72)</f>
         <v>8</v>
       </c>
-      <c r="O59" s="13" t="s">
+      <c r="O73" s="13" t="s">
         <v>132</v>
       </c>
-      <c r="P59" s="13">
-        <f>SUBTOTAL(9,P57:P58)</f>
+      <c r="P73" s="13">
+        <f>SUBTOTAL(9,P71:P72)</f>
         <v>7</v>
       </c>
-      <c r="R59" s="13" t="s">
+      <c r="R73" s="13" t="s">
         <v>132</v>
       </c>
-      <c r="S59" s="13">
-        <f>SUBTOTAL(9,S57:S58)</f>
+      <c r="S73" s="13">
+        <f>SUBTOTAL(9,S71:S72)</f>
         <v>7</v>
       </c>
-      <c r="T59" s="13" t="s">
+      <c r="T73" s="13" t="s">
         <v>132</v>
       </c>
-      <c r="Y59" s="13">
-        <f>SUBTOTAL(9,Y57:Y58)</f>
+      <c r="Y73" s="13">
+        <f>SUBTOTAL(9,Y71:Y72)</f>
         <v>8</v>
       </c>
     </row>
